--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,370 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123043424</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Forsby skog, Forsby skog, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>384579</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6216441</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123041890</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsby skog, Forsby skog, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>384833</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6216338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123048253</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>384791</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6216539</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,6 +1277,130 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123110343</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58156</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogshyddan S Kriks, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>384916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6216524</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123043424</v>
+        <v>123048253</v>
       </c>
       <c r="B4" t="n">
         <v>57629</v>
@@ -948,11 +948,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -965,17 +961,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384579</v>
+        <v>384791</v>
       </c>
       <c r="R4" t="n">
-        <v>6216441</v>
+        <v>6216539</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041890</v>
+        <v>123043424</v>
       </c>
       <c r="B5" t="n">
         <v>57629</v>
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384833</v>
+        <v>384579</v>
       </c>
       <c r="R5" t="n">
-        <v>6216338</v>
+        <v>6216441</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,9 +1124,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123048253</v>
+        <v>123041890</v>
       </c>
       <c r="B6" t="n">
         <v>57629</v>
@@ -1190,7 +1196,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1203,17 +1213,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384791</v>
+        <v>384833</v>
       </c>
       <c r="R6" t="n">
-        <v>6216539</v>
+        <v>6216338</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,19 +1250,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123048253</v>
+        <v>123043424</v>
       </c>
       <c r="B4" t="n">
         <v>57629</v>
@@ -948,7 +948,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -961,17 +965,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384791</v>
+        <v>384579</v>
       </c>
       <c r="R4" t="n">
-        <v>6216539</v>
+        <v>6216441</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123043424</v>
+        <v>123041890</v>
       </c>
       <c r="B5" t="n">
         <v>57629</v>
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384579</v>
+        <v>384833</v>
       </c>
       <c r="R5" t="n">
-        <v>6216441</v>
+        <v>6216338</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,19 +1128,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041890</v>
+        <v>123048253</v>
       </c>
       <c r="B6" t="n">
         <v>57629</v>
@@ -1196,11 +1190,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1213,17 +1203,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384833</v>
+        <v>384791</v>
       </c>
       <c r="R6" t="n">
-        <v>6216338</v>
+        <v>6216539</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,9 +1240,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123043424</v>
+        <v>123048253</v>
       </c>
       <c r="B4" t="n">
         <v>57629</v>
@@ -948,11 +948,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -965,17 +961,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384579</v>
+        <v>384791</v>
       </c>
       <c r="R4" t="n">
-        <v>6216441</v>
+        <v>6216539</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1157,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123048253</v>
+        <v>123043424</v>
       </c>
       <c r="B6" t="n">
         <v>57629</v>
@@ -1190,7 +1186,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1203,17 +1203,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384791</v>
+        <v>384579</v>
       </c>
       <c r="R6" t="n">
-        <v>6216539</v>
+        <v>6216441</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123048253</v>
+        <v>123043424</v>
       </c>
       <c r="B4" t="n">
         <v>57629</v>
@@ -948,7 +948,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -961,17 +965,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384791</v>
+        <v>384579</v>
       </c>
       <c r="R4" t="n">
-        <v>6216539</v>
+        <v>6216441</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041890</v>
+        <v>123048253</v>
       </c>
       <c r="B5" t="n">
         <v>57629</v>
@@ -1070,11 +1074,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1087,17 +1087,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384833</v>
+        <v>384791</v>
       </c>
       <c r="R5" t="n">
-        <v>6216338</v>
+        <v>6216539</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,9 +1124,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123043424</v>
+        <v>123041890</v>
       </c>
       <c r="B6" t="n">
         <v>57629</v>
@@ -1207,13 +1217,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384579</v>
+        <v>384833</v>
       </c>
       <c r="R6" t="n">
-        <v>6216441</v>
+        <v>6216338</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,19 +1250,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1401,6 +1401,2721 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123330248</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>384801</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6216415</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123322288</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57629</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Krika 2, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>384803</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6216452</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123330194</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>384879</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6216271</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123330284</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>384686</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6216321</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123330315</v>
+      </c>
+      <c r="B12" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>384685</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6216404</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123330183</v>
+      </c>
+      <c r="B13" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>384696</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6216241</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123330196</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>384879</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6216271</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123330258</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96992</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>384724</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6216417</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123330306</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78566</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>924</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>384733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6216385</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En bål mellan stora bålar med porlav</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123330282</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>384686</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6216321</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123330299</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96992</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>384718</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6216416</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123330257</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94865</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>384724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6216417</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123330210</v>
+      </c>
+      <c r="B20" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>384737</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6216302</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123330229</v>
+      </c>
+      <c r="B21" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>384694</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6216418</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123330259</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96992</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>384863</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6216260</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123330187</v>
+      </c>
+      <c r="B23" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>384730</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6216280</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123330199</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>384747</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6216370</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123330190</v>
+      </c>
+      <c r="B25" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>384703</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6216448</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123330226</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96992</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>384798</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6216268</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123330271</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80401</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>384715</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6216422</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123330301</v>
+      </c>
+      <c r="B28" t="n">
+        <v>77102</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1342</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bokvårtlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrenula nitida</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>384718</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6216416</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123330311</v>
+      </c>
+      <c r="B29" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>384830</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6216253</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123330269</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96992</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>384715</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6216422</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123330192</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96898</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>384693</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6216445</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123322284</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Krika 1, Sk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>384701</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6216470</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123330321</v>
+      </c>
+      <c r="B33" t="n">
+        <v>94776</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>384869</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6216249</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -3781,10 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330192</v>
+        <v>123322284</v>
       </c>
       <c r="B31" t="n">
-        <v>96898</v>
+        <v>57484</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,41 +3793,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2569</v>
+        <v>100048</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384693</v>
+        <v>384701</v>
       </c>
       <c r="R31" t="n">
-        <v>6216445</v>
+        <v>6216470</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3854,9 +3870,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3871,22 +3902,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123322284</v>
+        <v>123330321</v>
       </c>
       <c r="B32" t="n">
-        <v>57484</v>
+        <v>94776</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,57 +3926,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>384701</v>
+        <v>384869</v>
       </c>
       <c r="R32" t="n">
-        <v>6216470</v>
+        <v>6216249</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3972,24 +3987,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4004,26 +4004,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123330321</v>
+        <v>123330192</v>
       </c>
       <c r="B33" t="n">
-        <v>94776</v>
+        <v>96898</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>384869</v>
+        <v>384693</v>
       </c>
       <c r="R33" t="n">
-        <v>6216249</v>
+        <v>6216445</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4116,6 +4116,132 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123383860</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91356</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sydlig sotticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ischnoderma resinosum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Forsby, Sk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>384864</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6216297</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Västra Sönnarslöv</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula, Lars Salomon, Jan Svensson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -2450,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330299</v>
+        <v>123330257</v>
       </c>
       <c r="B18" t="n">
-        <v>96992</v>
+        <v>94865</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,21 +2466,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384718</v>
+        <v>384724</v>
       </c>
       <c r="R18" t="n">
-        <v>6216416</v>
+        <v>6216417</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330257</v>
+        <v>123330299</v>
       </c>
       <c r="B19" t="n">
-        <v>94865</v>
+        <v>96992</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384724</v>
+        <v>384718</v>
       </c>
       <c r="R19" t="n">
-        <v>6216417</v>
+        <v>6216416</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123043424</v>
+        <v>123041890</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384579</v>
+        <v>384833</v>
       </c>
       <c r="R4" t="n">
-        <v>6216441</v>
+        <v>6216338</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,19 +1002,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1034,7 @@
         <v>123048253</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1163,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041890</v>
+        <v>123043424</v>
       </c>
       <c r="B6" t="n">
-        <v>57629</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384833</v>
+        <v>384579</v>
       </c>
       <c r="R6" t="n">
-        <v>6216338</v>
+        <v>6216441</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,9 +1240,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
         <v>123110343</v>
       </c>
       <c r="B7" t="n">
-        <v>58156</v>
+        <v>58159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330248</v>
+        <v>123330199</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>94779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384801</v>
+        <v>384747</v>
       </c>
       <c r="R8" t="n">
-        <v>6216415</v>
+        <v>6216370</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123322288</v>
+        <v>123330187</v>
       </c>
       <c r="B9" t="n">
-        <v>57629</v>
+        <v>94779</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,53 +1517,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384803</v>
+        <v>384730</v>
       </c>
       <c r="R9" t="n">
-        <v>6216452</v>
+        <v>6216280</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,19 +1578,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1595,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330194</v>
+        <v>123322284</v>
       </c>
       <c r="B10" t="n">
-        <v>94776</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,41 +1619,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384879</v>
+        <v>384701</v>
       </c>
       <c r="R10" t="n">
-        <v>6216271</v>
+        <v>6216470</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,9 +1696,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,22 +1728,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330284</v>
+        <v>123330299</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>96995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1756,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,13 +1780,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384686</v>
+        <v>384718</v>
       </c>
       <c r="R11" t="n">
-        <v>6216321</v>
+        <v>6216416</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1833,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330315</v>
+        <v>123330284</v>
       </c>
       <c r="B12" t="n">
-        <v>94776</v>
+        <v>57851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,21 +1858,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,13 +1882,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384685</v>
+        <v>384686</v>
       </c>
       <c r="R12" t="n">
-        <v>6216404</v>
+        <v>6216321</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330183</v>
+        <v>123330315</v>
       </c>
       <c r="B13" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384696</v>
+        <v>384685</v>
       </c>
       <c r="R13" t="n">
-        <v>6216241</v>
+        <v>6216404</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2037,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330196</v>
+        <v>123330248</v>
       </c>
       <c r="B14" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384879</v>
+        <v>384801</v>
       </c>
       <c r="R14" t="n">
-        <v>6216271</v>
+        <v>6216415</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2139,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330258</v>
+        <v>123330210</v>
       </c>
       <c r="B15" t="n">
-        <v>96992</v>
+        <v>94779</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384724</v>
+        <v>384737</v>
       </c>
       <c r="R15" t="n">
-        <v>6216417</v>
+        <v>6216302</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2241,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330306</v>
+        <v>123330258</v>
       </c>
       <c r="B16" t="n">
-        <v>78566</v>
+        <v>96995</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,25 +2262,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2281,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384733</v>
+        <v>384724</v>
       </c>
       <c r="R16" t="n">
-        <v>6216385</v>
+        <v>6216417</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2317,11 +2326,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En bål mellan stora bålar med porlav</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330282</v>
+        <v>123330183</v>
       </c>
       <c r="B17" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384686</v>
+        <v>384696</v>
       </c>
       <c r="R17" t="n">
-        <v>6216321</v>
+        <v>6216241</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2453,7 +2457,7 @@
         <v>123330257</v>
       </c>
       <c r="B18" t="n">
-        <v>94865</v>
+        <v>94868</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330299</v>
+        <v>123330269</v>
       </c>
       <c r="B19" t="n">
-        <v>96992</v>
+        <v>96995</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384718</v>
+        <v>384715</v>
       </c>
       <c r="R19" t="n">
-        <v>6216416</v>
+        <v>6216422</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330210</v>
+        <v>123330196</v>
       </c>
       <c r="B20" t="n">
-        <v>94776</v>
+        <v>57497</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,25 +2670,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2694,13 +2698,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384737</v>
+        <v>384879</v>
       </c>
       <c r="R20" t="n">
-        <v>6216302</v>
+        <v>6216271</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330229</v>
+        <v>123330190</v>
       </c>
       <c r="B21" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384694</v>
+        <v>384703</v>
       </c>
       <c r="R21" t="n">
-        <v>6216418</v>
+        <v>6216448</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2858,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330259</v>
+        <v>123330282</v>
       </c>
       <c r="B22" t="n">
-        <v>96992</v>
+        <v>94779</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,21 +2878,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384863</v>
+        <v>384686</v>
       </c>
       <c r="R22" t="n">
-        <v>6216260</v>
+        <v>6216321</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2960,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330187</v>
+        <v>123330321</v>
       </c>
       <c r="B23" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384730</v>
+        <v>384869</v>
       </c>
       <c r="R23" t="n">
-        <v>6216280</v>
+        <v>6216249</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3062,10 +3066,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330199</v>
+        <v>123322288</v>
       </c>
       <c r="B24" t="n">
-        <v>94776</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3074,41 +3078,53 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384747</v>
+        <v>384803</v>
       </c>
       <c r="R24" t="n">
-        <v>6216370</v>
+        <v>6216452</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3135,9 +3151,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3152,22 +3178,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330190</v>
+        <v>123330194</v>
       </c>
       <c r="B25" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384703</v>
+        <v>384879</v>
       </c>
       <c r="R25" t="n">
-        <v>6216448</v>
+        <v>6216271</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3266,10 +3292,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330226</v>
+        <v>123330229</v>
       </c>
       <c r="B26" t="n">
-        <v>96992</v>
+        <v>94779</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3282,21 +3308,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3306,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384798</v>
+        <v>384694</v>
       </c>
       <c r="R26" t="n">
-        <v>6216268</v>
+        <v>6216418</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3368,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330271</v>
+        <v>123330259</v>
       </c>
       <c r="B27" t="n">
-        <v>80401</v>
+        <v>96995</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3384,21 +3410,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384715</v>
+        <v>384863</v>
       </c>
       <c r="R27" t="n">
-        <v>6216422</v>
+        <v>6216260</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3470,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330301</v>
+        <v>123330271</v>
       </c>
       <c r="B28" t="n">
-        <v>77102</v>
+        <v>80404</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3482,25 +3508,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3510,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384718</v>
+        <v>384715</v>
       </c>
       <c r="R28" t="n">
-        <v>6216416</v>
+        <v>6216422</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3546,11 +3572,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,7 +3601,7 @@
         <v>123330311</v>
       </c>
       <c r="B29" t="n">
-        <v>94776</v>
+        <v>94779</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3679,10 +3700,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330269</v>
+        <v>123330226</v>
       </c>
       <c r="B30" t="n">
-        <v>96992</v>
+        <v>96995</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3719,10 +3740,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384715</v>
+        <v>384798</v>
       </c>
       <c r="R30" t="n">
-        <v>6216422</v>
+        <v>6216268</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3781,10 +3802,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123322284</v>
+        <v>123330301</v>
       </c>
       <c r="B31" t="n">
-        <v>57484</v>
+        <v>77105</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3797,53 +3818,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100048</v>
+        <v>1342</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384701</v>
+        <v>384718</v>
       </c>
       <c r="R31" t="n">
-        <v>6216470</v>
+        <v>6216416</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3870,24 +3875,14 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3902,26 +3897,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123330321</v>
+        <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>94776</v>
+        <v>96901</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3930,21 +3925,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3954,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>384869</v>
+        <v>384693</v>
       </c>
       <c r="R32" t="n">
-        <v>6216249</v>
+        <v>6216445</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4016,53 +4011,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123330192</v>
+        <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>96898</v>
+        <v>91359</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2569</v>
+        <v>2023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>384693</v>
+        <v>384864</v>
       </c>
       <c r="R33" t="n">
-        <v>6216445</v>
+        <v>6216297</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4100,28 +4098,49 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula, Lars Salomon, Jan Svensson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123383860</v>
+        <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>91356</v>
+        <v>78569</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4134,40 +4153,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2023</v>
+        <v>924</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>384864</v>
+        <v>384733</v>
       </c>
       <c r="R34" t="n">
-        <v>6216297</v>
+        <v>6216385</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4199,45 +4215,29 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>En bål mellan stora bålar med porlav</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Fagus sylvatica</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula, Lars Salomon, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123041890</v>
+        <v>123043424</v>
       </c>
       <c r="B4" t="n">
         <v>57632</v>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384833</v>
+        <v>384579</v>
       </c>
       <c r="R4" t="n">
-        <v>6216338</v>
+        <v>6216441</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,9 +1002,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123048253</v>
+        <v>123041890</v>
       </c>
       <c r="B5" t="n">
         <v>57632</v>
@@ -1064,7 +1074,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1077,17 +1091,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384791</v>
+        <v>384833</v>
       </c>
       <c r="R5" t="n">
-        <v>6216539</v>
+        <v>6216338</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,19 +1128,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123043424</v>
+        <v>123048253</v>
       </c>
       <c r="B6" t="n">
         <v>57632</v>
@@ -1186,11 +1190,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1203,17 +1203,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384579</v>
+        <v>384791</v>
       </c>
       <c r="R6" t="n">
-        <v>6216441</v>
+        <v>6216539</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330199</v>
+        <v>123330194</v>
       </c>
       <c r="B8" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384747</v>
+        <v>384879</v>
       </c>
       <c r="R8" t="n">
-        <v>6216370</v>
+        <v>6216271</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330187</v>
+        <v>123330315</v>
       </c>
       <c r="B9" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384730</v>
+        <v>384685</v>
       </c>
       <c r="R9" t="n">
-        <v>6216280</v>
+        <v>6216404</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123322284</v>
+        <v>123330190</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>94781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,57 +1619,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384701</v>
+        <v>384703</v>
       </c>
       <c r="R10" t="n">
-        <v>6216470</v>
+        <v>6216448</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,24 +1680,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,22 +1697,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330299</v>
+        <v>123330183</v>
       </c>
       <c r="B11" t="n">
-        <v>96995</v>
+        <v>94781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384718</v>
+        <v>384696</v>
       </c>
       <c r="R11" t="n">
-        <v>6216416</v>
+        <v>6216241</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1842,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330284</v>
+        <v>123330248</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,20 +1823,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1882,13 +1851,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384686</v>
+        <v>384801</v>
       </c>
       <c r="R12" t="n">
-        <v>6216321</v>
+        <v>6216415</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1944,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330315</v>
+        <v>123330196</v>
       </c>
       <c r="B13" t="n">
-        <v>94779</v>
+        <v>57497</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,25 +1925,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1984,13 +1953,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384685</v>
+        <v>384879</v>
       </c>
       <c r="R13" t="n">
-        <v>6216404</v>
+        <v>6216271</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,17 +2008,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330248</v>
+        <v>123330259</v>
       </c>
       <c r="B14" t="n">
-        <v>57497</v>
+        <v>96997</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384801</v>
+        <v>384863</v>
       </c>
       <c r="R14" t="n">
-        <v>6216415</v>
+        <v>6216260</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,17 +2110,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330210</v>
+        <v>123330321</v>
       </c>
       <c r="B15" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384737</v>
+        <v>384869</v>
       </c>
       <c r="R15" t="n">
-        <v>6216302</v>
+        <v>6216249</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2250,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330258</v>
+        <v>123330284</v>
       </c>
       <c r="B16" t="n">
-        <v>96995</v>
+        <v>57851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2290,13 +2259,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384724</v>
+        <v>384686</v>
       </c>
       <c r="R16" t="n">
-        <v>6216417</v>
+        <v>6216321</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330183</v>
+        <v>123330226</v>
       </c>
       <c r="B17" t="n">
-        <v>94779</v>
+        <v>96997</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,21 +2337,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384696</v>
+        <v>384798</v>
       </c>
       <c r="R17" t="n">
-        <v>6216241</v>
+        <v>6216268</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2454,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330257</v>
+        <v>123330299</v>
       </c>
       <c r="B18" t="n">
-        <v>94868</v>
+        <v>96997</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2439,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384724</v>
+        <v>384718</v>
       </c>
       <c r="R18" t="n">
-        <v>6216417</v>
+        <v>6216416</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2549,17 +2518,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330269</v>
+        <v>123330187</v>
       </c>
       <c r="B19" t="n">
-        <v>96995</v>
+        <v>94781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2572,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2596,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384715</v>
+        <v>384730</v>
       </c>
       <c r="R19" t="n">
-        <v>6216422</v>
+        <v>6216280</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2651,17 +2620,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330196</v>
+        <v>123322284</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,16 +2643,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2691,20 +2660,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384879</v>
+        <v>384701</v>
       </c>
       <c r="R20" t="n">
-        <v>6216271</v>
+        <v>6216470</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,9 +2716,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,22 +2748,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330190</v>
+        <v>123330271</v>
       </c>
       <c r="B21" t="n">
-        <v>94779</v>
+        <v>80406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2776,21 +2776,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384703</v>
+        <v>384715</v>
       </c>
       <c r="R21" t="n">
-        <v>6216448</v>
+        <v>6216422</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330282</v>
+        <v>123330301</v>
       </c>
       <c r="B22" t="n">
-        <v>94779</v>
+        <v>77107</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2874,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384686</v>
+        <v>384718</v>
       </c>
       <c r="R22" t="n">
-        <v>6216321</v>
+        <v>6216416</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2938,6 +2938,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330321</v>
+        <v>123330258</v>
       </c>
       <c r="B23" t="n">
-        <v>94779</v>
+        <v>96997</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,21 +2985,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3004,10 +3009,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384869</v>
+        <v>384724</v>
       </c>
       <c r="R23" t="n">
-        <v>6216249</v>
+        <v>6216417</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3066,10 +3071,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123322288</v>
+        <v>123330229</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
+        <v>94781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3078,53 +3083,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384803</v>
+        <v>384694</v>
       </c>
       <c r="R24" t="n">
-        <v>6216452</v>
+        <v>6216418</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3151,19 +3144,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3178,22 +3161,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330194</v>
+        <v>123330282</v>
       </c>
       <c r="B25" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384879</v>
+        <v>384686</v>
       </c>
       <c r="R25" t="n">
-        <v>6216271</v>
+        <v>6216321</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3285,17 +3268,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330229</v>
+        <v>123330210</v>
       </c>
       <c r="B26" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3332,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384694</v>
+        <v>384737</v>
       </c>
       <c r="R26" t="n">
-        <v>6216418</v>
+        <v>6216302</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3387,17 +3370,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330259</v>
+        <v>123330269</v>
       </c>
       <c r="B27" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3434,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384863</v>
+        <v>384715</v>
       </c>
       <c r="R27" t="n">
-        <v>6216260</v>
+        <v>6216422</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3496,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330271</v>
+        <v>123330257</v>
       </c>
       <c r="B28" t="n">
-        <v>80404</v>
+        <v>94870</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,21 +3495,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384715</v>
+        <v>384724</v>
       </c>
       <c r="R28" t="n">
-        <v>6216422</v>
+        <v>6216417</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3598,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330311</v>
+        <v>123322288</v>
       </c>
       <c r="B29" t="n">
-        <v>94779</v>
+        <v>57632</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,41 +3593,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384830</v>
+        <v>384803</v>
       </c>
       <c r="R29" t="n">
-        <v>6216253</v>
+        <v>6216452</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3671,9 +3666,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,22 +3693,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330226</v>
+        <v>123330199</v>
       </c>
       <c r="B30" t="n">
-        <v>96995</v>
+        <v>94781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3716,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3740,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384798</v>
+        <v>384747</v>
       </c>
       <c r="R30" t="n">
-        <v>6216268</v>
+        <v>6216370</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3795,17 +3800,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330301</v>
+        <v>123330311</v>
       </c>
       <c r="B31" t="n">
-        <v>77105</v>
+        <v>94781</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3814,25 +3819,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3842,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384718</v>
+        <v>384830</v>
       </c>
       <c r="R31" t="n">
-        <v>6216416</v>
+        <v>6216253</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3878,11 +3883,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96901</v>
+        <v>96903</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>91359</v>
+        <v>91361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>78569</v>
+        <v>78571</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041890</v>
+        <v>123048253</v>
       </c>
       <c r="B5" t="n">
         <v>57632</v>
@@ -1074,11 +1074,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1091,17 +1087,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384833</v>
+        <v>384791</v>
       </c>
       <c r="R5" t="n">
-        <v>6216338</v>
+        <v>6216539</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,9 +1124,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123048253</v>
+        <v>123041890</v>
       </c>
       <c r="B6" t="n">
         <v>57632</v>
@@ -1190,7 +1196,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1203,17 +1213,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384791</v>
+        <v>384833</v>
       </c>
       <c r="R6" t="n">
-        <v>6216539</v>
+        <v>6216338</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,19 +1250,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330194</v>
+        <v>123330190</v>
       </c>
       <c r="B8" t="n">
-        <v>94781</v>
+        <v>94787</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384879</v>
+        <v>384703</v>
       </c>
       <c r="R8" t="n">
-        <v>6216271</v>
+        <v>6216448</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330315</v>
+        <v>123322288</v>
       </c>
       <c r="B9" t="n">
-        <v>94781</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,41 +1517,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384685</v>
+        <v>384803</v>
       </c>
       <c r="R9" t="n">
-        <v>6216404</v>
+        <v>6216452</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,9 +1590,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,22 +1617,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330190</v>
+        <v>123330282</v>
       </c>
       <c r="B10" t="n">
-        <v>94781</v>
+        <v>94787</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384703</v>
+        <v>384686</v>
       </c>
       <c r="R10" t="n">
-        <v>6216448</v>
+        <v>6216321</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330183</v>
+        <v>123330210</v>
       </c>
       <c r="B11" t="n">
-        <v>94781</v>
+        <v>94787</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384696</v>
+        <v>384737</v>
       </c>
       <c r="R11" t="n">
-        <v>6216241</v>
+        <v>6216302</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1804,17 +1826,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330248</v>
+        <v>123330269</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>97003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,25 +1845,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,13 +1873,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384801</v>
+        <v>384715</v>
       </c>
       <c r="R12" t="n">
-        <v>6216415</v>
+        <v>6216422</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330196</v>
+        <v>123330299</v>
       </c>
       <c r="B13" t="n">
-        <v>57497</v>
+        <v>97003</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,25 +1947,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384879</v>
+        <v>384718</v>
       </c>
       <c r="R13" t="n">
-        <v>6216271</v>
+        <v>6216416</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330259</v>
+        <v>123330271</v>
       </c>
       <c r="B14" t="n">
-        <v>96997</v>
+        <v>80407</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384863</v>
+        <v>384715</v>
       </c>
       <c r="R14" t="n">
-        <v>6216260</v>
+        <v>6216422</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2110,17 +2132,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330321</v>
+        <v>123330187</v>
       </c>
       <c r="B15" t="n">
-        <v>94781</v>
+        <v>94787</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384869</v>
+        <v>384730</v>
       </c>
       <c r="R15" t="n">
-        <v>6216249</v>
+        <v>6216280</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2212,17 +2234,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330284</v>
+        <v>123330311</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>94787</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2257,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,13 +2281,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384686</v>
+        <v>384830</v>
       </c>
       <c r="R16" t="n">
-        <v>6216321</v>
+        <v>6216253</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330226</v>
+        <v>123330257</v>
       </c>
       <c r="B17" t="n">
-        <v>96997</v>
+        <v>94876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,21 +2359,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384798</v>
+        <v>384724</v>
       </c>
       <c r="R17" t="n">
-        <v>6216268</v>
+        <v>6216417</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330299</v>
+        <v>123322284</v>
       </c>
       <c r="B18" t="n">
-        <v>96997</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,41 +2457,57 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384718</v>
+        <v>384701</v>
       </c>
       <c r="R18" t="n">
-        <v>6216416</v>
+        <v>6216470</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2496,9 +2534,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,22 +2566,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330187</v>
+        <v>123330196</v>
       </c>
       <c r="B19" t="n">
-        <v>94781</v>
+        <v>57497</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,25 +2590,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2618,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384730</v>
+        <v>384879</v>
       </c>
       <c r="R19" t="n">
-        <v>6216280</v>
+        <v>6216271</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123322284</v>
+        <v>123330183</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>94787</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,57 +2692,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384701</v>
+        <v>384696</v>
       </c>
       <c r="R20" t="n">
-        <v>6216470</v>
+        <v>6216241</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,24 +2753,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,22 +2770,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330271</v>
+        <v>123330194</v>
       </c>
       <c r="B21" t="n">
-        <v>80406</v>
+        <v>94787</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2776,21 +2798,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230185</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2822,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384715</v>
+        <v>384879</v>
       </c>
       <c r="R21" t="n">
-        <v>6216422</v>
+        <v>6216271</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2862,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330301</v>
+        <v>123330321</v>
       </c>
       <c r="B22" t="n">
-        <v>77107</v>
+        <v>94787</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,25 +2896,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2902,10 +2924,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R22" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2940,11 +2962,6 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2962,17 +2979,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330258</v>
+        <v>123330315</v>
       </c>
       <c r="B23" t="n">
-        <v>96997</v>
+        <v>94787</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2985,21 +3002,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3009,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384724</v>
+        <v>384685</v>
       </c>
       <c r="R23" t="n">
-        <v>6216417</v>
+        <v>6216404</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3064,17 +3081,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330229</v>
+        <v>123330248</v>
       </c>
       <c r="B24" t="n">
-        <v>94781</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,25 +3100,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3111,13 +3128,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384694</v>
+        <v>384801</v>
       </c>
       <c r="R24" t="n">
-        <v>6216418</v>
+        <v>6216415</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330282</v>
+        <v>123330301</v>
       </c>
       <c r="B25" t="n">
-        <v>94781</v>
+        <v>77108</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3185,25 +3202,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384686</v>
+        <v>384718</v>
       </c>
       <c r="R25" t="n">
-        <v>6216321</v>
+        <v>6216416</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3249,6 +3266,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3275,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330210</v>
+        <v>123330259</v>
       </c>
       <c r="B26" t="n">
-        <v>94781</v>
+        <v>97003</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3291,21 +3313,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384737</v>
+        <v>384863</v>
       </c>
       <c r="R26" t="n">
-        <v>6216302</v>
+        <v>6216260</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3377,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330269</v>
+        <v>123330229</v>
       </c>
       <c r="B27" t="n">
-        <v>96997</v>
+        <v>94787</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3393,21 +3415,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3417,10 +3439,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384715</v>
+        <v>384694</v>
       </c>
       <c r="R27" t="n">
-        <v>6216422</v>
+        <v>6216418</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3479,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330257</v>
+        <v>123330226</v>
       </c>
       <c r="B28" t="n">
-        <v>94870</v>
+        <v>97003</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,21 +3517,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3519,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384724</v>
+        <v>384798</v>
       </c>
       <c r="R28" t="n">
-        <v>6216417</v>
+        <v>6216268</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3581,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123322288</v>
+        <v>123330199</v>
       </c>
       <c r="B29" t="n">
-        <v>57632</v>
+        <v>94787</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,53 +3615,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384803</v>
+        <v>384747</v>
       </c>
       <c r="R29" t="n">
-        <v>6216452</v>
+        <v>6216370</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3666,19 +3676,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,22 +3693,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330199</v>
+        <v>123330258</v>
       </c>
       <c r="B30" t="n">
-        <v>94781</v>
+        <v>97003</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384747</v>
+        <v>384724</v>
       </c>
       <c r="R30" t="n">
-        <v>6216370</v>
+        <v>6216417</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330311</v>
+        <v>123330284</v>
       </c>
       <c r="B31" t="n">
-        <v>94781</v>
+        <v>57851</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384830</v>
+        <v>384686</v>
       </c>
       <c r="R31" t="n">
-        <v>6216253</v>
+        <v>6216321</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96903</v>
+        <v>96909</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
         <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>91361</v>
+        <v>91367</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>78571</v>
+        <v>78572</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330257</v>
+        <v>123330194</v>
       </c>
       <c r="B28" t="n">
-        <v>94879</v>
+        <v>94790</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,21 +3517,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384724</v>
+        <v>384879</v>
       </c>
       <c r="R28" t="n">
-        <v>6216417</v>
+        <v>6216271</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330194</v>
+        <v>123330311</v>
       </c>
       <c r="B29" t="n">
         <v>94790</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384879</v>
+        <v>384830</v>
       </c>
       <c r="R29" t="n">
-        <v>6216271</v>
+        <v>6216253</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330311</v>
+        <v>123330257</v>
       </c>
       <c r="B30" t="n">
-        <v>94790</v>
+        <v>94879</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384830</v>
+        <v>384724</v>
       </c>
       <c r="R30" t="n">
-        <v>6216253</v>
+        <v>6216417</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>123043424</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041890</v>
+        <v>123048253</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,11 +1074,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1091,17 +1087,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384833</v>
+        <v>384791</v>
       </c>
       <c r="R5" t="n">
-        <v>6216338</v>
+        <v>6216539</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,9 +1124,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123048253</v>
+        <v>123041890</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,7 +1196,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1203,17 +1213,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384791</v>
+        <v>384833</v>
       </c>
       <c r="R6" t="n">
-        <v>6216539</v>
+        <v>6216338</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,19 +1250,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1282,7 @@
         <v>123110343</v>
       </c>
       <c r="B7" t="n">
-        <v>58159</v>
+        <v>58165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330199</v>
+        <v>123330282</v>
       </c>
       <c r="B8" t="n">
-        <v>94790</v>
+        <v>94807</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384747</v>
+        <v>384686</v>
       </c>
       <c r="R8" t="n">
-        <v>6216370</v>
+        <v>6216321</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330248</v>
+        <v>123330229</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>94807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384801</v>
+        <v>384694</v>
       </c>
       <c r="R9" t="n">
-        <v>6216415</v>
+        <v>6216418</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330321</v>
+        <v>123330183</v>
       </c>
       <c r="B10" t="n">
-        <v>94790</v>
+        <v>94807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384869</v>
+        <v>384696</v>
       </c>
       <c r="R10" t="n">
-        <v>6216249</v>
+        <v>6216241</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330258</v>
+        <v>123330196</v>
       </c>
       <c r="B11" t="n">
-        <v>97006</v>
+        <v>57503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384724</v>
+        <v>384879</v>
       </c>
       <c r="R11" t="n">
-        <v>6216417</v>
+        <v>6216271</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330259</v>
+        <v>123330258</v>
       </c>
       <c r="B12" t="n">
-        <v>97006</v>
+        <v>97023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384863</v>
+        <v>384724</v>
       </c>
       <c r="R12" t="n">
-        <v>6216260</v>
+        <v>6216417</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330187</v>
+        <v>123330321</v>
       </c>
       <c r="B13" t="n">
-        <v>94790</v>
+        <v>94807</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384730</v>
+        <v>384869</v>
       </c>
       <c r="R13" t="n">
-        <v>6216280</v>
+        <v>6216249</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2018,7 +2018,7 @@
         <v>123330315</v>
       </c>
       <c r="B14" t="n">
-        <v>94790</v>
+        <v>94807</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330269</v>
+        <v>123330226</v>
       </c>
       <c r="B15" t="n">
-        <v>97006</v>
+        <v>97023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384715</v>
+        <v>384798</v>
       </c>
       <c r="R15" t="n">
-        <v>6216422</v>
+        <v>6216268</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330229</v>
+        <v>123330269</v>
       </c>
       <c r="B16" t="n">
-        <v>94790</v>
+        <v>97023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384694</v>
+        <v>384715</v>
       </c>
       <c r="R16" t="n">
-        <v>6216418</v>
+        <v>6216422</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330210</v>
+        <v>123330257</v>
       </c>
       <c r="B17" t="n">
-        <v>94790</v>
+        <v>94896</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384737</v>
+        <v>384724</v>
       </c>
       <c r="R17" t="n">
-        <v>6216302</v>
+        <v>6216417</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123322284</v>
+        <v>123330271</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>80416</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,57 +2435,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384701</v>
+        <v>384715</v>
       </c>
       <c r="R18" t="n">
-        <v>6216470</v>
+        <v>6216422</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,24 +2496,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,22 +2513,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330271</v>
+        <v>123330299</v>
       </c>
       <c r="B19" t="n">
-        <v>80410</v>
+        <v>97023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2572,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2596,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384715</v>
+        <v>384718</v>
       </c>
       <c r="R19" t="n">
-        <v>6216422</v>
+        <v>6216416</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2658,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330196</v>
+        <v>123330248</v>
       </c>
       <c r="B20" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384879</v>
+        <v>384801</v>
       </c>
       <c r="R20" t="n">
-        <v>6216271</v>
+        <v>6216415</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2760,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123322288</v>
+        <v>123330194</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>94807</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,53 +2741,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384803</v>
+        <v>384879</v>
       </c>
       <c r="R21" t="n">
-        <v>6216452</v>
+        <v>6216271</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2845,19 +2802,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,22 +2819,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330183</v>
+        <v>123330259</v>
       </c>
       <c r="B22" t="n">
-        <v>94790</v>
+        <v>97023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,21 +2847,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2924,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384696</v>
+        <v>384863</v>
       </c>
       <c r="R22" t="n">
-        <v>6216241</v>
+        <v>6216260</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2986,10 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330226</v>
+        <v>123330284</v>
       </c>
       <c r="B23" t="n">
-        <v>97006</v>
+        <v>57857</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,21 +2949,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3026,13 +2973,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384798</v>
+        <v>384686</v>
       </c>
       <c r="R23" t="n">
-        <v>6216268</v>
+        <v>6216321</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330284</v>
+        <v>123330210</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>94807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,13 +3075,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384686</v>
+        <v>384737</v>
       </c>
       <c r="R24" t="n">
-        <v>6216321</v>
+        <v>6216302</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3190,10 +3137,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330301</v>
+        <v>123330190</v>
       </c>
       <c r="B25" t="n">
-        <v>77111</v>
+        <v>94807</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,25 +3149,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384718</v>
+        <v>384703</v>
       </c>
       <c r="R25" t="n">
-        <v>6216416</v>
+        <v>6216448</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3266,11 +3213,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330282</v>
+        <v>123322288</v>
       </c>
       <c r="B26" t="n">
-        <v>94790</v>
+        <v>57638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3309,41 +3251,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384686</v>
+        <v>384803</v>
       </c>
       <c r="R26" t="n">
-        <v>6216321</v>
+        <v>6216452</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3370,9 +3324,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,22 +3351,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330299</v>
+        <v>123330199</v>
       </c>
       <c r="B27" t="n">
-        <v>97006</v>
+        <v>94807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3415,21 +3379,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3439,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384718</v>
+        <v>384747</v>
       </c>
       <c r="R27" t="n">
-        <v>6216416</v>
+        <v>6216370</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3501,10 +3465,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330194</v>
+        <v>123330301</v>
       </c>
       <c r="B28" t="n">
-        <v>94790</v>
+        <v>77117</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,25 +3477,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384879</v>
+        <v>384718</v>
       </c>
       <c r="R28" t="n">
-        <v>6216271</v>
+        <v>6216416</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3577,6 +3541,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3606,7 +3575,7 @@
         <v>123330311</v>
       </c>
       <c r="B29" t="n">
-        <v>94790</v>
+        <v>94807</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3705,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330257</v>
+        <v>123330187</v>
       </c>
       <c r="B30" t="n">
-        <v>94879</v>
+        <v>94807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3690,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384724</v>
+        <v>384730</v>
       </c>
       <c r="R30" t="n">
-        <v>6216417</v>
+        <v>6216280</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3807,10 +3776,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330190</v>
+        <v>123322284</v>
       </c>
       <c r="B31" t="n">
-        <v>94790</v>
+        <v>57493</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3819,41 +3788,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384703</v>
+        <v>384701</v>
       </c>
       <c r="R31" t="n">
-        <v>6216448</v>
+        <v>6216470</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3880,9 +3865,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96912</v>
+        <v>96929</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>91387</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>78575</v>
+        <v>78581</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123043424</v>
+        <v>123048253</v>
       </c>
       <c r="B4" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,11 +948,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -965,17 +961,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384579</v>
+        <v>384791</v>
       </c>
       <c r="R4" t="n">
-        <v>6216441</v>
+        <v>6216539</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123048253</v>
+        <v>123043424</v>
       </c>
       <c r="B5" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,7 +1070,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1087,17 +1087,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384791</v>
+        <v>384579</v>
       </c>
       <c r="R5" t="n">
-        <v>6216539</v>
+        <v>6216441</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,7 +1166,7 @@
         <v>123041890</v>
       </c>
       <c r="B6" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>123110343</v>
       </c>
       <c r="B7" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330282</v>
+        <v>123330258</v>
       </c>
       <c r="B8" t="n">
-        <v>94807</v>
+        <v>97039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384686</v>
+        <v>384724</v>
       </c>
       <c r="R8" t="n">
-        <v>6216321</v>
+        <v>6216417</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330229</v>
+        <v>123330311</v>
       </c>
       <c r="B9" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384694</v>
+        <v>384830</v>
       </c>
       <c r="R9" t="n">
-        <v>6216418</v>
+        <v>6216253</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330183</v>
+        <v>123330229</v>
       </c>
       <c r="B10" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384696</v>
+        <v>384694</v>
       </c>
       <c r="R10" t="n">
-        <v>6216241</v>
+        <v>6216418</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330196</v>
+        <v>123330271</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
+        <v>80421</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384879</v>
+        <v>384715</v>
       </c>
       <c r="R11" t="n">
-        <v>6216271</v>
+        <v>6216422</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330258</v>
+        <v>123330183</v>
       </c>
       <c r="B12" t="n">
-        <v>97023</v>
+        <v>94813</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384724</v>
+        <v>384696</v>
       </c>
       <c r="R12" t="n">
-        <v>6216417</v>
+        <v>6216241</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330321</v>
+        <v>123330226</v>
       </c>
       <c r="B13" t="n">
-        <v>94807</v>
+        <v>97039</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384869</v>
+        <v>384798</v>
       </c>
       <c r="R13" t="n">
-        <v>6216249</v>
+        <v>6216268</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330315</v>
+        <v>123330284</v>
       </c>
       <c r="B14" t="n">
-        <v>94807</v>
+        <v>57860</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384685</v>
+        <v>384686</v>
       </c>
       <c r="R14" t="n">
-        <v>6216404</v>
+        <v>6216321</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330226</v>
+        <v>123330190</v>
       </c>
       <c r="B15" t="n">
-        <v>97023</v>
+        <v>94813</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384798</v>
+        <v>384703</v>
       </c>
       <c r="R15" t="n">
-        <v>6216268</v>
+        <v>6216448</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330269</v>
+        <v>123330210</v>
       </c>
       <c r="B16" t="n">
-        <v>97023</v>
+        <v>94813</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384715</v>
+        <v>384737</v>
       </c>
       <c r="R16" t="n">
-        <v>6216422</v>
+        <v>6216302</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330257</v>
+        <v>123330194</v>
       </c>
       <c r="B17" t="n">
-        <v>94896</v>
+        <v>94813</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384724</v>
+        <v>384879</v>
       </c>
       <c r="R17" t="n">
-        <v>6216417</v>
+        <v>6216271</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330271</v>
+        <v>123330259</v>
       </c>
       <c r="B18" t="n">
-        <v>80416</v>
+        <v>97039</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384715</v>
+        <v>384863</v>
       </c>
       <c r="R18" t="n">
-        <v>6216422</v>
+        <v>6216260</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330299</v>
+        <v>123322288</v>
       </c>
       <c r="B19" t="n">
-        <v>97023</v>
+        <v>57641</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,41 +2537,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384718</v>
+        <v>384803</v>
       </c>
       <c r="R19" t="n">
-        <v>6216416</v>
+        <v>6216452</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2598,9 +2610,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,22 +2637,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330248</v>
+        <v>123330196</v>
       </c>
       <c r="B20" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384801</v>
+        <v>384879</v>
       </c>
       <c r="R20" t="n">
-        <v>6216415</v>
+        <v>6216271</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2729,10 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330194</v>
+        <v>123330321</v>
       </c>
       <c r="B21" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384879</v>
+        <v>384869</v>
       </c>
       <c r="R21" t="n">
-        <v>6216271</v>
+        <v>6216249</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2831,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330259</v>
+        <v>123322284</v>
       </c>
       <c r="B22" t="n">
-        <v>97023</v>
+        <v>57496</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,41 +2865,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>100048</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384863</v>
+        <v>384701</v>
       </c>
       <c r="R22" t="n">
-        <v>6216260</v>
+        <v>6216470</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2904,9 +2942,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,22 +2974,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330284</v>
+        <v>123330248</v>
       </c>
       <c r="B23" t="n">
-        <v>57857</v>
+        <v>57506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2945,20 +2998,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2973,13 +3026,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384686</v>
+        <v>384801</v>
       </c>
       <c r="R23" t="n">
-        <v>6216321</v>
+        <v>6216415</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330210</v>
+        <v>123330299</v>
       </c>
       <c r="B24" t="n">
-        <v>94807</v>
+        <v>97039</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,21 +3104,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3075,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384737</v>
+        <v>384718</v>
       </c>
       <c r="R24" t="n">
-        <v>6216302</v>
+        <v>6216416</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3137,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330190</v>
+        <v>123330257</v>
       </c>
       <c r="B25" t="n">
-        <v>94807</v>
+        <v>94902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,21 +3206,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384703</v>
+        <v>384724</v>
       </c>
       <c r="R25" t="n">
-        <v>6216448</v>
+        <v>6216417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3239,10 +3292,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123322288</v>
+        <v>123330187</v>
       </c>
       <c r="B26" t="n">
-        <v>57638</v>
+        <v>94813</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,53 +3304,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384803</v>
+        <v>384730</v>
       </c>
       <c r="R26" t="n">
-        <v>6216452</v>
+        <v>6216280</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,19 +3365,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,22 +3382,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330199</v>
+        <v>123330301</v>
       </c>
       <c r="B27" t="n">
-        <v>94807</v>
+        <v>77122</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,25 +3406,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3403,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384747</v>
+        <v>384718</v>
       </c>
       <c r="R27" t="n">
-        <v>6216370</v>
+        <v>6216416</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3439,6 +3470,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3465,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330301</v>
+        <v>123330282</v>
       </c>
       <c r="B28" t="n">
-        <v>77117</v>
+        <v>94813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,25 +3513,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3505,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384718</v>
+        <v>384686</v>
       </c>
       <c r="R28" t="n">
-        <v>6216416</v>
+        <v>6216321</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3541,11 +3577,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3572,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330311</v>
+        <v>123330199</v>
       </c>
       <c r="B29" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384830</v>
+        <v>384747</v>
       </c>
       <c r="R29" t="n">
-        <v>6216253</v>
+        <v>6216370</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3674,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330187</v>
+        <v>123330269</v>
       </c>
       <c r="B30" t="n">
-        <v>94807</v>
+        <v>97039</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3714,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384730</v>
+        <v>384715</v>
       </c>
       <c r="R30" t="n">
-        <v>6216280</v>
+        <v>6216422</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3776,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123322284</v>
+        <v>123330315</v>
       </c>
       <c r="B31" t="n">
-        <v>57493</v>
+        <v>94813</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,57 +3819,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384701</v>
+        <v>384685</v>
       </c>
       <c r="R31" t="n">
-        <v>6216470</v>
+        <v>6216404</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3865,24 +3880,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96929</v>
+        <v>96945</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>91387</v>
+        <v>91392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>78581</v>
+        <v>78586</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1282,7 +1282,7 @@
         <v>123110343</v>
       </c>
       <c r="B7" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330258</v>
+        <v>123330284</v>
       </c>
       <c r="B8" t="n">
-        <v>97039</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384724</v>
+        <v>384686</v>
       </c>
       <c r="R8" t="n">
-        <v>6216417</v>
+        <v>6216321</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330311</v>
+        <v>123330229</v>
       </c>
       <c r="B9" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384830</v>
+        <v>384694</v>
       </c>
       <c r="R9" t="n">
-        <v>6216253</v>
+        <v>6216418</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330229</v>
+        <v>123330210</v>
       </c>
       <c r="B10" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384694</v>
+        <v>384737</v>
       </c>
       <c r="R10" t="n">
-        <v>6216418</v>
+        <v>6216302</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330271</v>
+        <v>123330311</v>
       </c>
       <c r="B11" t="n">
-        <v>80421</v>
+        <v>94815</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384715</v>
+        <v>384830</v>
       </c>
       <c r="R11" t="n">
-        <v>6216422</v>
+        <v>6216253</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330183</v>
+        <v>123322284</v>
       </c>
       <c r="B12" t="n">
-        <v>94813</v>
+        <v>57497</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,41 +1823,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384696</v>
+        <v>384701</v>
       </c>
       <c r="R12" t="n">
-        <v>6216241</v>
+        <v>6216470</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,9 +1900,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330226</v>
+        <v>123330199</v>
       </c>
       <c r="B13" t="n">
-        <v>97039</v>
+        <v>94815</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384798</v>
+        <v>384747</v>
       </c>
       <c r="R13" t="n">
-        <v>6216268</v>
+        <v>6216370</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330284</v>
+        <v>123330248</v>
       </c>
       <c r="B14" t="n">
-        <v>57860</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,20 +2058,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2055,13 +2086,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384686</v>
+        <v>384801</v>
       </c>
       <c r="R14" t="n">
-        <v>6216321</v>
+        <v>6216415</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330190</v>
+        <v>123330257</v>
       </c>
       <c r="B15" t="n">
-        <v>94813</v>
+        <v>94904</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384703</v>
+        <v>384724</v>
       </c>
       <c r="R15" t="n">
-        <v>6216448</v>
+        <v>6216417</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330210</v>
+        <v>123330194</v>
       </c>
       <c r="B16" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384737</v>
+        <v>384879</v>
       </c>
       <c r="R16" t="n">
-        <v>6216302</v>
+        <v>6216271</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2321,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330194</v>
+        <v>123330259</v>
       </c>
       <c r="B17" t="n">
-        <v>94813</v>
+        <v>97041</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,21 +2368,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384879</v>
+        <v>384863</v>
       </c>
       <c r="R17" t="n">
-        <v>6216271</v>
+        <v>6216260</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2423,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330259</v>
+        <v>123330269</v>
       </c>
       <c r="B18" t="n">
-        <v>97039</v>
+        <v>97041</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384863</v>
+        <v>384715</v>
       </c>
       <c r="R18" t="n">
-        <v>6216260</v>
+        <v>6216422</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2525,10 +2556,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123322288</v>
+        <v>123330196</v>
       </c>
       <c r="B19" t="n">
-        <v>57641</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,16 +2572,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,32 +2589,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384803</v>
+        <v>384879</v>
       </c>
       <c r="R19" t="n">
-        <v>6216452</v>
+        <v>6216271</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,19 +2629,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,22 +2646,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330196</v>
+        <v>123330315</v>
       </c>
       <c r="B20" t="n">
-        <v>57506</v>
+        <v>94815</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2661,25 +2670,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2689,13 +2698,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384879</v>
+        <v>384685</v>
       </c>
       <c r="R20" t="n">
-        <v>6216271</v>
+        <v>6216404</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330321</v>
+        <v>123330187</v>
       </c>
       <c r="B21" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384869</v>
+        <v>384730</v>
       </c>
       <c r="R21" t="n">
-        <v>6216249</v>
+        <v>6216280</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2853,10 +2862,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123322284</v>
+        <v>123322288</v>
       </c>
       <c r="B22" t="n">
-        <v>57496</v>
+        <v>57642</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,16 +2878,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2891,11 +2900,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
@@ -2905,14 +2910,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384701</v>
+        <v>384803</v>
       </c>
       <c r="R22" t="n">
-        <v>6216470</v>
+        <v>6216452</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2955,11 +2960,6 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330248</v>
+        <v>123330190</v>
       </c>
       <c r="B23" t="n">
-        <v>57506</v>
+        <v>94815</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2998,25 +2998,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3026,13 +3026,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384801</v>
+        <v>384703</v>
       </c>
       <c r="R23" t="n">
-        <v>6216415</v>
+        <v>6216448</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>123330299</v>
       </c>
       <c r="B24" t="n">
-        <v>97039</v>
+        <v>97041</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330257</v>
+        <v>123330183</v>
       </c>
       <c r="B25" t="n">
-        <v>94902</v>
+        <v>94815</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384724</v>
+        <v>384696</v>
       </c>
       <c r="R25" t="n">
-        <v>6216417</v>
+        <v>6216241</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330187</v>
+        <v>123330226</v>
       </c>
       <c r="B26" t="n">
-        <v>94813</v>
+        <v>97041</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,21 +3308,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384730</v>
+        <v>384798</v>
       </c>
       <c r="R26" t="n">
-        <v>6216280</v>
+        <v>6216268</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3394,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330301</v>
+        <v>123330258</v>
       </c>
       <c r="B27" t="n">
-        <v>77122</v>
+        <v>97041</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3406,25 +3406,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384718</v>
+        <v>384724</v>
       </c>
       <c r="R27" t="n">
-        <v>6216416</v>
+        <v>6216417</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3470,11 +3470,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330282</v>
+        <v>123330301</v>
       </c>
       <c r="B28" t="n">
-        <v>94813</v>
+        <v>77124</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,25 +3508,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384686</v>
+        <v>384718</v>
       </c>
       <c r="R28" t="n">
-        <v>6216321</v>
+        <v>6216416</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3577,6 +3572,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330199</v>
+        <v>123330321</v>
       </c>
       <c r="B29" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384747</v>
+        <v>384869</v>
       </c>
       <c r="R29" t="n">
-        <v>6216370</v>
+        <v>6216249</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330269</v>
+        <v>123330282</v>
       </c>
       <c r="B30" t="n">
-        <v>97039</v>
+        <v>94815</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384715</v>
+        <v>384686</v>
       </c>
       <c r="R30" t="n">
-        <v>6216422</v>
+        <v>6216321</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330315</v>
+        <v>123330271</v>
       </c>
       <c r="B31" t="n">
-        <v>94813</v>
+        <v>80423</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384685</v>
+        <v>384715</v>
       </c>
       <c r="R31" t="n">
-        <v>6216404</v>
+        <v>6216422</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96945</v>
+        <v>96947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>123383860</v>
       </c>
       <c r="B33" t="n">
-        <v>91392</v>
+        <v>91394</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>123330306</v>
       </c>
       <c r="B34" t="n">
-        <v>78586</v>
+        <v>78588</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -3088,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330299</v>
+        <v>123330183</v>
       </c>
       <c r="B24" t="n">
-        <v>97041</v>
+        <v>94815</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384718</v>
+        <v>384696</v>
       </c>
       <c r="R24" t="n">
-        <v>6216416</v>
+        <v>6216241</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330183</v>
+        <v>123330299</v>
       </c>
       <c r="B25" t="n">
-        <v>94815</v>
+        <v>97041</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384696</v>
+        <v>384718</v>
       </c>
       <c r="R25" t="n">
-        <v>6216241</v>
+        <v>6216416</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330301</v>
+        <v>123330321</v>
       </c>
       <c r="B28" t="n">
-        <v>77124</v>
+        <v>94815</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3508,25 +3508,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R28" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3572,11 +3572,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330321</v>
+        <v>123330301</v>
       </c>
       <c r="B29" t="n">
-        <v>94815</v>
+        <v>77124</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,25 +3610,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,10 +3638,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384869</v>
+        <v>384718</v>
       </c>
       <c r="R29" t="n">
-        <v>6216249</v>
+        <v>6216416</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3679,6 +3674,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -3088,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330183</v>
+        <v>123330299</v>
       </c>
       <c r="B24" t="n">
-        <v>94815</v>
+        <v>97041</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,21 +3104,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384696</v>
+        <v>384718</v>
       </c>
       <c r="R24" t="n">
-        <v>6216241</v>
+        <v>6216416</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330299</v>
+        <v>123330183</v>
       </c>
       <c r="B25" t="n">
-        <v>97041</v>
+        <v>94815</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,21 +3206,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384718</v>
+        <v>384696</v>
       </c>
       <c r="R25" t="n">
-        <v>6216416</v>
+        <v>6216241</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330321</v>
+        <v>123330301</v>
       </c>
       <c r="B28" t="n">
-        <v>94815</v>
+        <v>77124</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3508,25 +3508,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384869</v>
+        <v>384718</v>
       </c>
       <c r="R28" t="n">
-        <v>6216249</v>
+        <v>6216416</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3572,6 +3572,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330301</v>
+        <v>123330321</v>
       </c>
       <c r="B29" t="n">
-        <v>77124</v>
+        <v>94815</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,25 +3615,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3638,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R29" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3674,11 +3679,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330284</v>
+        <v>123330194</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>95323</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384686</v>
+        <v>384879</v>
       </c>
       <c r="R8" t="n">
-        <v>6216321</v>
+        <v>6216271</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330229</v>
+        <v>123330259</v>
       </c>
       <c r="B9" t="n">
-        <v>94815</v>
+        <v>96759</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384694</v>
+        <v>384863</v>
       </c>
       <c r="R9" t="n">
-        <v>6216418</v>
+        <v>6216260</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330210</v>
+        <v>123330282</v>
       </c>
       <c r="B10" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384737</v>
+        <v>384686</v>
       </c>
       <c r="R10" t="n">
-        <v>6216302</v>
+        <v>6216321</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330311</v>
+        <v>123330301</v>
       </c>
       <c r="B11" t="n">
-        <v>94815</v>
+        <v>77124</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384830</v>
+        <v>384718</v>
       </c>
       <c r="R11" t="n">
-        <v>6216253</v>
+        <v>6216416</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1785,6 +1785,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123322284</v>
+        <v>123330190</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>95323</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,57 +1828,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384701</v>
+        <v>384703</v>
       </c>
       <c r="R12" t="n">
-        <v>6216470</v>
+        <v>6216448</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,24 +1889,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1906,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330199</v>
+        <v>123330311</v>
       </c>
       <c r="B13" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384747</v>
+        <v>384830</v>
       </c>
       <c r="R13" t="n">
-        <v>6216370</v>
+        <v>6216253</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2046,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330248</v>
+        <v>123330199</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2032,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,13 +2060,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384801</v>
+        <v>384747</v>
       </c>
       <c r="R14" t="n">
-        <v>6216415</v>
+        <v>6216370</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2148,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330257</v>
+        <v>123330226</v>
       </c>
       <c r="B15" t="n">
-        <v>94904</v>
+        <v>96759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384724</v>
+        <v>384798</v>
       </c>
       <c r="R15" t="n">
-        <v>6216417</v>
+        <v>6216268</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2250,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330194</v>
+        <v>123330210</v>
       </c>
       <c r="B16" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384879</v>
+        <v>384737</v>
       </c>
       <c r="R16" t="n">
-        <v>6216271</v>
+        <v>6216302</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2352,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330259</v>
+        <v>123322288</v>
       </c>
       <c r="B17" t="n">
-        <v>97041</v>
+        <v>57642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,41 +2338,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2606</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384863</v>
+        <v>384803</v>
       </c>
       <c r="R17" t="n">
-        <v>6216260</v>
+        <v>6216452</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,9 +2411,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,22 +2438,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330269</v>
+        <v>123330271</v>
       </c>
       <c r="B18" t="n">
-        <v>97041</v>
+        <v>80423</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2466,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330196</v>
+        <v>123330187</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2596,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384879</v>
+        <v>384730</v>
       </c>
       <c r="R19" t="n">
-        <v>6216271</v>
+        <v>6216280</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,10 +2654,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330315</v>
+        <v>123330284</v>
       </c>
       <c r="B20" t="n">
-        <v>94815</v>
+        <v>57861</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,21 +2670,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,13 +2694,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384685</v>
+        <v>384686</v>
       </c>
       <c r="R20" t="n">
-        <v>6216404</v>
+        <v>6216321</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330187</v>
+        <v>123330315</v>
       </c>
       <c r="B21" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384730</v>
+        <v>384685</v>
       </c>
       <c r="R21" t="n">
-        <v>6216280</v>
+        <v>6216404</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2862,10 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123322288</v>
+        <v>123330229</v>
       </c>
       <c r="B22" t="n">
-        <v>57642</v>
+        <v>95323</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2874,53 +2870,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384803</v>
+        <v>384694</v>
       </c>
       <c r="R22" t="n">
-        <v>6216452</v>
+        <v>6216418</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2947,19 +2931,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,22 +2948,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330190</v>
+        <v>123330183</v>
       </c>
       <c r="B23" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3026,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384703</v>
+        <v>384696</v>
       </c>
       <c r="R23" t="n">
-        <v>6216448</v>
+        <v>6216241</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3088,10 +3062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330299</v>
+        <v>123330321</v>
       </c>
       <c r="B24" t="n">
-        <v>97041</v>
+        <v>95323</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,21 +3078,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R24" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3190,10 +3164,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330183</v>
+        <v>123330299</v>
       </c>
       <c r="B25" t="n">
-        <v>94815</v>
+        <v>96759</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,21 +3180,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3204,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384696</v>
+        <v>384718</v>
       </c>
       <c r="R25" t="n">
-        <v>6216241</v>
+        <v>6216416</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3292,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330226</v>
+        <v>123330196</v>
       </c>
       <c r="B26" t="n">
-        <v>97041</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3304,25 +3278,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3332,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384798</v>
+        <v>384879</v>
       </c>
       <c r="R26" t="n">
-        <v>6216268</v>
+        <v>6216271</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3397,7 +3371,7 @@
         <v>123330258</v>
       </c>
       <c r="B27" t="n">
-        <v>97041</v>
+        <v>96759</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330301</v>
+        <v>123330269</v>
       </c>
       <c r="B28" t="n">
-        <v>77124</v>
+        <v>96759</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3508,25 +3482,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384718</v>
+        <v>384715</v>
       </c>
       <c r="R28" t="n">
-        <v>6216416</v>
+        <v>6216422</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3572,11 +3546,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,10 +3572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330321</v>
+        <v>123330248</v>
       </c>
       <c r="B29" t="n">
-        <v>94815</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,25 +3584,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,13 +3612,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384869</v>
+        <v>384801</v>
       </c>
       <c r="R29" t="n">
-        <v>6216249</v>
+        <v>6216415</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3705,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330282</v>
+        <v>123322284</v>
       </c>
       <c r="B30" t="n">
-        <v>94815</v>
+        <v>57497</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3717,41 +3686,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384686</v>
+        <v>384701</v>
       </c>
       <c r="R30" t="n">
-        <v>6216321</v>
+        <v>6216470</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3778,9 +3763,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3795,22 +3795,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330271</v>
+        <v>123330257</v>
       </c>
       <c r="B31" t="n">
-        <v>80423</v>
+        <v>95412</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384715</v>
+        <v>384724</v>
       </c>
       <c r="R31" t="n">
-        <v>6216422</v>
+        <v>6216417</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3912,7 +3912,7 @@
         <v>123330192</v>
       </c>
       <c r="B32" t="n">
-        <v>96947</v>
+        <v>96707</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330194</v>
+        <v>123330258</v>
       </c>
       <c r="B8" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384879</v>
+        <v>384724</v>
       </c>
       <c r="R8" t="n">
-        <v>6216271</v>
+        <v>6216417</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330259</v>
+        <v>123330284</v>
       </c>
       <c r="B9" t="n">
-        <v>96759</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384863</v>
+        <v>384686</v>
       </c>
       <c r="R9" t="n">
-        <v>6216260</v>
+        <v>6216321</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330282</v>
+        <v>123330311</v>
       </c>
       <c r="B10" t="n">
         <v>95323</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384686</v>
+        <v>384830</v>
       </c>
       <c r="R10" t="n">
-        <v>6216321</v>
+        <v>6216253</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330301</v>
+        <v>123330321</v>
       </c>
       <c r="B11" t="n">
-        <v>77124</v>
+        <v>95323</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R11" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1785,11 +1785,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330190</v>
+        <v>123330199</v>
       </c>
       <c r="B12" t="n">
         <v>95323</v>
@@ -1856,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384703</v>
+        <v>384747</v>
       </c>
       <c r="R12" t="n">
-        <v>6216448</v>
+        <v>6216370</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1918,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330311</v>
+        <v>123330269</v>
       </c>
       <c r="B13" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1929,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384830</v>
+        <v>384715</v>
       </c>
       <c r="R13" t="n">
-        <v>6216253</v>
+        <v>6216422</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2020,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330199</v>
+        <v>123330257</v>
       </c>
       <c r="B14" t="n">
-        <v>95323</v>
+        <v>95412</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384747</v>
+        <v>384724</v>
       </c>
       <c r="R14" t="n">
-        <v>6216370</v>
+        <v>6216417</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2122,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330226</v>
+        <v>123322284</v>
       </c>
       <c r="B15" t="n">
-        <v>96759</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,41 +2129,57 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384798</v>
+        <v>384701</v>
       </c>
       <c r="R15" t="n">
-        <v>6216268</v>
+        <v>6216470</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,9 +2206,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,19 +2238,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330210</v>
+        <v>123330190</v>
       </c>
       <c r="B16" t="n">
         <v>95323</v>
@@ -2264,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384737</v>
+        <v>384703</v>
       </c>
       <c r="R16" t="n">
-        <v>6216302</v>
+        <v>6216448</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2326,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123322288</v>
+        <v>123330229</v>
       </c>
       <c r="B17" t="n">
-        <v>57642</v>
+        <v>95323</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,53 +2364,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384803</v>
+        <v>384694</v>
       </c>
       <c r="R17" t="n">
-        <v>6216452</v>
+        <v>6216418</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,19 +2425,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,22 +2442,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330271</v>
+        <v>123330299</v>
       </c>
       <c r="B18" t="n">
-        <v>80423</v>
+        <v>96759</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2490,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384715</v>
+        <v>384718</v>
       </c>
       <c r="R18" t="n">
-        <v>6216422</v>
+        <v>6216416</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2552,7 +2556,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330187</v>
+        <v>123330194</v>
       </c>
       <c r="B19" t="n">
         <v>95323</v>
@@ -2592,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384730</v>
+        <v>384879</v>
       </c>
       <c r="R19" t="n">
-        <v>6216280</v>
+        <v>6216271</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330284</v>
+        <v>123330187</v>
       </c>
       <c r="B20" t="n">
-        <v>57861</v>
+        <v>95323</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2670,21 +2674,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2694,13 +2698,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384686</v>
+        <v>384730</v>
       </c>
       <c r="R20" t="n">
-        <v>6216321</v>
+        <v>6216280</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330315</v>
+        <v>123330301</v>
       </c>
       <c r="B21" t="n">
-        <v>95323</v>
+        <v>77124</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,25 +2772,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384685</v>
+        <v>384718</v>
       </c>
       <c r="R21" t="n">
-        <v>6216404</v>
+        <v>6216416</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2832,6 +2836,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330229</v>
+        <v>123330196</v>
       </c>
       <c r="B22" t="n">
-        <v>95323</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,25 +2879,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,13 +2907,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384694</v>
+        <v>384879</v>
       </c>
       <c r="R22" t="n">
-        <v>6216418</v>
+        <v>6216271</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330183</v>
+        <v>123330226</v>
       </c>
       <c r="B23" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2976,21 +2985,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +3009,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384696</v>
+        <v>384798</v>
       </c>
       <c r="R23" t="n">
-        <v>6216241</v>
+        <v>6216268</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3062,10 +3071,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330321</v>
+        <v>123330271</v>
       </c>
       <c r="B24" t="n">
-        <v>95323</v>
+        <v>80423</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3078,21 +3087,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2810</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3102,10 +3111,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384869</v>
+        <v>384715</v>
       </c>
       <c r="R24" t="n">
-        <v>6216249</v>
+        <v>6216422</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3164,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330299</v>
+        <v>123330282</v>
       </c>
       <c r="B25" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,21 +3189,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3204,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384718</v>
+        <v>384686</v>
       </c>
       <c r="R25" t="n">
-        <v>6216416</v>
+        <v>6216321</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3266,10 +3275,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330196</v>
+        <v>123330183</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3278,25 +3287,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3306,13 +3315,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384879</v>
+        <v>384696</v>
       </c>
       <c r="R26" t="n">
-        <v>6216271</v>
+        <v>6216241</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3368,10 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330258</v>
+        <v>123330315</v>
       </c>
       <c r="B27" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3384,21 +3393,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384724</v>
+        <v>384685</v>
       </c>
       <c r="R27" t="n">
-        <v>6216417</v>
+        <v>6216404</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3470,7 +3479,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330269</v>
+        <v>123330259</v>
       </c>
       <c r="B28" t="n">
         <v>96759</v>
@@ -3510,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384715</v>
+        <v>384863</v>
       </c>
       <c r="R28" t="n">
-        <v>6216422</v>
+        <v>6216260</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3674,10 +3683,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123322284</v>
+        <v>123322288</v>
       </c>
       <c r="B30" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,16 +3699,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3712,11 +3721,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
@@ -3726,14 +3731,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384701</v>
+        <v>384803</v>
       </c>
       <c r="R30" t="n">
-        <v>6216470</v>
+        <v>6216452</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3776,11 +3781,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330257</v>
+        <v>123330210</v>
       </c>
       <c r="B31" t="n">
-        <v>95412</v>
+        <v>95323</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384724</v>
+        <v>384737</v>
       </c>
       <c r="R31" t="n">
-        <v>6216417</v>
+        <v>6216302</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330258</v>
+        <v>123330248</v>
       </c>
       <c r="B8" t="n">
-        <v>96759</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384724</v>
+        <v>384801</v>
       </c>
       <c r="R8" t="n">
-        <v>6216417</v>
+        <v>6216415</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330284</v>
+        <v>123330311</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>95323</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384686</v>
+        <v>384830</v>
       </c>
       <c r="R9" t="n">
-        <v>6216321</v>
+        <v>6216253</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330311</v>
+        <v>123322284</v>
       </c>
       <c r="B10" t="n">
-        <v>95323</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,41 +1619,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384830</v>
+        <v>384701</v>
       </c>
       <c r="R10" t="n">
-        <v>6216253</v>
+        <v>6216470</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,9 +1696,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,19 +1728,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330321</v>
+        <v>123330315</v>
       </c>
       <c r="B11" t="n">
         <v>95323</v>
@@ -1749,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384869</v>
+        <v>384685</v>
       </c>
       <c r="R11" t="n">
-        <v>6216249</v>
+        <v>6216404</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1913,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330269</v>
+        <v>123330257</v>
       </c>
       <c r="B13" t="n">
-        <v>96759</v>
+        <v>95412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384715</v>
+        <v>384724</v>
       </c>
       <c r="R13" t="n">
-        <v>6216422</v>
+        <v>6216417</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2015,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330257</v>
+        <v>123330259</v>
       </c>
       <c r="B14" t="n">
-        <v>95412</v>
+        <v>96759</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,21 +2062,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384724</v>
+        <v>384863</v>
       </c>
       <c r="R14" t="n">
-        <v>6216417</v>
+        <v>6216260</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123322284</v>
+        <v>123330190</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>95323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,57 +2160,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384701</v>
+        <v>384703</v>
       </c>
       <c r="R15" t="n">
-        <v>6216470</v>
+        <v>6216448</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,24 +2221,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,22 +2238,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330190</v>
+        <v>123330258</v>
       </c>
       <c r="B16" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384703</v>
+        <v>384724</v>
       </c>
       <c r="R16" t="n">
-        <v>6216448</v>
+        <v>6216417</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330229</v>
+        <v>123330301</v>
       </c>
       <c r="B17" t="n">
-        <v>95323</v>
+        <v>77124</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,25 +2364,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384694</v>
+        <v>384718</v>
       </c>
       <c r="R17" t="n">
-        <v>6216418</v>
+        <v>6216416</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,6 +2428,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330299</v>
+        <v>123330271</v>
       </c>
       <c r="B18" t="n">
-        <v>96759</v>
+        <v>80423</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2475,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384718</v>
+        <v>384715</v>
       </c>
       <c r="R18" t="n">
-        <v>6216416</v>
+        <v>6216422</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2556,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330194</v>
+        <v>123322288</v>
       </c>
       <c r="B19" t="n">
-        <v>95323</v>
+        <v>57642</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,41 +2573,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384879</v>
+        <v>384803</v>
       </c>
       <c r="R19" t="n">
-        <v>6216271</v>
+        <v>6216452</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,9 +2646,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,19 +2673,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330187</v>
+        <v>123330194</v>
       </c>
       <c r="B20" t="n">
         <v>95323</v>
@@ -2698,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384730</v>
+        <v>384879</v>
       </c>
       <c r="R20" t="n">
-        <v>6216280</v>
+        <v>6216271</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2760,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330301</v>
+        <v>123330269</v>
       </c>
       <c r="B21" t="n">
-        <v>77124</v>
+        <v>96759</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,25 +2799,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384718</v>
+        <v>384715</v>
       </c>
       <c r="R21" t="n">
-        <v>6216416</v>
+        <v>6216422</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2836,11 +2863,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330196</v>
+        <v>123330284</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,20 +2901,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2907,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384879</v>
+        <v>384686</v>
       </c>
       <c r="R22" t="n">
-        <v>6216271</v>
+        <v>6216321</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330226</v>
+        <v>123330210</v>
       </c>
       <c r="B23" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2985,21 +3007,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3009,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384798</v>
+        <v>384737</v>
       </c>
       <c r="R23" t="n">
-        <v>6216268</v>
+        <v>6216302</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3071,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330271</v>
+        <v>123330187</v>
       </c>
       <c r="B24" t="n">
-        <v>80423</v>
+        <v>95323</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3087,21 +3109,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3111,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384715</v>
+        <v>384730</v>
       </c>
       <c r="R24" t="n">
-        <v>6216422</v>
+        <v>6216280</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3173,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330282</v>
+        <v>123330299</v>
       </c>
       <c r="B25" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,21 +3211,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3213,10 +3235,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384686</v>
+        <v>384718</v>
       </c>
       <c r="R25" t="n">
-        <v>6216321</v>
+        <v>6216416</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3275,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330183</v>
+        <v>123330226</v>
       </c>
       <c r="B26" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3291,21 +3313,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3315,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384696</v>
+        <v>384798</v>
       </c>
       <c r="R26" t="n">
-        <v>6216241</v>
+        <v>6216268</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3377,7 +3399,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330315</v>
+        <v>123330321</v>
       </c>
       <c r="B27" t="n">
         <v>95323</v>
@@ -3417,10 +3439,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384685</v>
+        <v>384869</v>
       </c>
       <c r="R27" t="n">
-        <v>6216404</v>
+        <v>6216249</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3479,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330259</v>
+        <v>123330229</v>
       </c>
       <c r="B28" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,21 +3517,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3519,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384863</v>
+        <v>384694</v>
       </c>
       <c r="R28" t="n">
-        <v>6216260</v>
+        <v>6216418</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3581,7 +3603,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330248</v>
+        <v>123330196</v>
       </c>
       <c r="B29" t="n">
         <v>57507</v>
@@ -3621,10 +3643,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384801</v>
+        <v>384879</v>
       </c>
       <c r="R29" t="n">
-        <v>6216415</v>
+        <v>6216271</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3683,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123322288</v>
+        <v>123330282</v>
       </c>
       <c r="B30" t="n">
-        <v>57642</v>
+        <v>95323</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,53 +3717,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384803</v>
+        <v>384686</v>
       </c>
       <c r="R30" t="n">
-        <v>6216452</v>
+        <v>6216321</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3768,19 +3778,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3795,19 +3795,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330210</v>
+        <v>123330183</v>
       </c>
       <c r="B31" t="n">
         <v>95323</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384737</v>
+        <v>384696</v>
       </c>
       <c r="R31" t="n">
-        <v>6216302</v>
+        <v>6216241</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330248</v>
+        <v>123330259</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>96759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384801</v>
+        <v>384863</v>
       </c>
       <c r="R8" t="n">
-        <v>6216415</v>
+        <v>6216260</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330311</v>
+        <v>123330183</v>
       </c>
       <c r="B9" t="n">
         <v>95323</v>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384830</v>
+        <v>384696</v>
       </c>
       <c r="R9" t="n">
-        <v>6216253</v>
+        <v>6216241</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123322284</v>
+        <v>123330196</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1640,36 +1640,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384701</v>
+        <v>384879</v>
       </c>
       <c r="R10" t="n">
-        <v>6216470</v>
+        <v>6216271</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,24 +1680,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,12 +1697,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1842,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330199</v>
+        <v>123322288</v>
       </c>
       <c r="B12" t="n">
-        <v>95323</v>
+        <v>57642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,41 +1823,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384747</v>
+        <v>384803</v>
       </c>
       <c r="R12" t="n">
-        <v>6216370</v>
+        <v>6216452</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,9 +1896,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1923,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330257</v>
+        <v>123330258</v>
       </c>
       <c r="B13" t="n">
-        <v>95412</v>
+        <v>96759</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,7 +2037,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330259</v>
+        <v>123330226</v>
       </c>
       <c r="B14" t="n">
         <v>96759</v>
@@ -2086,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384863</v>
+        <v>384798</v>
       </c>
       <c r="R14" t="n">
-        <v>6216260</v>
+        <v>6216268</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2148,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330190</v>
+        <v>123322284</v>
       </c>
       <c r="B15" t="n">
-        <v>95323</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,41 +2151,57 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384703</v>
+        <v>384701</v>
       </c>
       <c r="R15" t="n">
-        <v>6216448</v>
+        <v>6216470</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,9 +2228,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,22 +2260,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330258</v>
+        <v>123330282</v>
       </c>
       <c r="B16" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2290,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384724</v>
+        <v>384686</v>
       </c>
       <c r="R16" t="n">
-        <v>6216417</v>
+        <v>6216321</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2352,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330301</v>
+        <v>123330321</v>
       </c>
       <c r="B17" t="n">
-        <v>77124</v>
+        <v>95323</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,25 +2386,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384718</v>
+        <v>384869</v>
       </c>
       <c r="R17" t="n">
-        <v>6216416</v>
+        <v>6216249</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,11 +2450,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330271</v>
+        <v>123330199</v>
       </c>
       <c r="B18" t="n">
-        <v>80423</v>
+        <v>95323</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2475,21 +2492,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384715</v>
+        <v>384747</v>
       </c>
       <c r="R18" t="n">
-        <v>6216422</v>
+        <v>6216370</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2561,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123322288</v>
+        <v>123330301</v>
       </c>
       <c r="B19" t="n">
-        <v>57642</v>
+        <v>77124</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,49 +2594,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>1342</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384803</v>
+        <v>384718</v>
       </c>
       <c r="R19" t="n">
-        <v>6216452</v>
+        <v>6216416</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,19 +2651,14 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>08:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,19 +2673,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330194</v>
+        <v>123330311</v>
       </c>
       <c r="B20" t="n">
         <v>95323</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384879</v>
+        <v>384830</v>
       </c>
       <c r="R20" t="n">
-        <v>6216271</v>
+        <v>6216253</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330269</v>
+        <v>123330248</v>
       </c>
       <c r="B21" t="n">
-        <v>96759</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384715</v>
+        <v>384801</v>
       </c>
       <c r="R21" t="n">
-        <v>6216422</v>
+        <v>6216415</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330284</v>
+        <v>123330271</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>80423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384686</v>
+        <v>384715</v>
       </c>
       <c r="R22" t="n">
-        <v>6216321</v>
+        <v>6216422</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330210</v>
+        <v>123330299</v>
       </c>
       <c r="B23" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384737</v>
+        <v>384718</v>
       </c>
       <c r="R23" t="n">
-        <v>6216302</v>
+        <v>6216416</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330299</v>
+        <v>123330194</v>
       </c>
       <c r="B25" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384718</v>
+        <v>384879</v>
       </c>
       <c r="R25" t="n">
-        <v>6216416</v>
+        <v>6216271</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330226</v>
+        <v>123330190</v>
       </c>
       <c r="B26" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384798</v>
+        <v>384703</v>
       </c>
       <c r="R26" t="n">
-        <v>6216268</v>
+        <v>6216448</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330321</v>
+        <v>123330284</v>
       </c>
       <c r="B27" t="n">
-        <v>95323</v>
+        <v>57861</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384869</v>
+        <v>384686</v>
       </c>
       <c r="R27" t="n">
-        <v>6216249</v>
+        <v>6216321</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330196</v>
+        <v>123330269</v>
       </c>
       <c r="B29" t="n">
-        <v>57507</v>
+        <v>96759</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,25 +3615,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384879</v>
+        <v>384715</v>
       </c>
       <c r="R29" t="n">
-        <v>6216271</v>
+        <v>6216422</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330282</v>
+        <v>123330210</v>
       </c>
       <c r="B30" t="n">
         <v>95323</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384686</v>
+        <v>384737</v>
       </c>
       <c r="R30" t="n">
-        <v>6216321</v>
+        <v>6216302</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330183</v>
+        <v>123330257</v>
       </c>
       <c r="B31" t="n">
-        <v>95323</v>
+        <v>95412</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384696</v>
+        <v>384724</v>
       </c>
       <c r="R31" t="n">
-        <v>6216241</v>
+        <v>6216417</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123322284</v>
+        <v>123330321</v>
       </c>
       <c r="B15" t="n">
-        <v>57497</v>
+        <v>95323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,57 +2151,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384701</v>
+        <v>384869</v>
       </c>
       <c r="R15" t="n">
-        <v>6216470</v>
+        <v>6216249</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,24 +2212,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,22 +2229,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330282</v>
+        <v>123322284</v>
       </c>
       <c r="B16" t="n">
-        <v>95323</v>
+        <v>57497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,41 +2253,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384686</v>
+        <v>384701</v>
       </c>
       <c r="R16" t="n">
-        <v>6216321</v>
+        <v>6216470</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2345,9 +2330,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,19 +2362,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330321</v>
+        <v>123330282</v>
       </c>
       <c r="B17" t="n">
         <v>95323</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384869</v>
+        <v>384686</v>
       </c>
       <c r="R17" t="n">
-        <v>6216249</v>
+        <v>6216321</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330301</v>
+        <v>123330311</v>
       </c>
       <c r="B19" t="n">
-        <v>77124</v>
+        <v>95323</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,25 +2590,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384718</v>
+        <v>384830</v>
       </c>
       <c r="R19" t="n">
-        <v>6216416</v>
+        <v>6216253</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,11 +2654,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330311</v>
+        <v>123330301</v>
       </c>
       <c r="B20" t="n">
-        <v>95323</v>
+        <v>77124</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2697,25 +2692,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384830</v>
+        <v>384718</v>
       </c>
       <c r="R20" t="n">
-        <v>6216253</v>
+        <v>6216416</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2761,6 +2756,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330248</v>
+        <v>123330271</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>80423</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384801</v>
+        <v>384715</v>
       </c>
       <c r="R21" t="n">
-        <v>6216415</v>
+        <v>6216422</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330271</v>
+        <v>123330248</v>
       </c>
       <c r="B22" t="n">
-        <v>80423</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,25 +2901,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384715</v>
+        <v>384801</v>
       </c>
       <c r="R22" t="n">
-        <v>6216422</v>
+        <v>6216415</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123330259</v>
+        <v>123322288</v>
       </c>
       <c r="B8" t="n">
-        <v>96759</v>
+        <v>57642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,41 +1415,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384863</v>
+        <v>384803</v>
       </c>
       <c r="R8" t="n">
-        <v>6216260</v>
+        <v>6216452</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,9 +1488,19 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,22 +1515,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330183</v>
+        <v>123330258</v>
       </c>
       <c r="B9" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,21 +1543,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384696</v>
+        <v>384724</v>
       </c>
       <c r="R9" t="n">
-        <v>6216241</v>
+        <v>6216417</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,17 +1622,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330196</v>
+        <v>123330311</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,13 +1669,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384879</v>
+        <v>384830</v>
       </c>
       <c r="R10" t="n">
-        <v>6216271</v>
+        <v>6216253</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330315</v>
+        <v>123330190</v>
       </c>
       <c r="B11" t="n">
         <v>95323</v>
@@ -1749,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384685</v>
+        <v>384703</v>
       </c>
       <c r="R11" t="n">
-        <v>6216404</v>
+        <v>6216448</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1804,17 +1826,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123322288</v>
+        <v>123330226</v>
       </c>
       <c r="B12" t="n">
-        <v>57642</v>
+        <v>96759</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,53 +1845,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384803</v>
+        <v>384798</v>
       </c>
       <c r="R12" t="n">
-        <v>6216452</v>
+        <v>6216268</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,19 +1906,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,19 +1923,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330258</v>
+        <v>123330299</v>
       </c>
       <c r="B13" t="n">
         <v>96759</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384724</v>
+        <v>384718</v>
       </c>
       <c r="R13" t="n">
-        <v>6216417</v>
+        <v>6216416</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330226</v>
+        <v>123330183</v>
       </c>
       <c r="B14" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384798</v>
+        <v>384696</v>
       </c>
       <c r="R14" t="n">
-        <v>6216268</v>
+        <v>6216241</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330321</v>
+        <v>123330257</v>
       </c>
       <c r="B15" t="n">
-        <v>95323</v>
+        <v>95412</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384869</v>
+        <v>384724</v>
       </c>
       <c r="R15" t="n">
-        <v>6216249</v>
+        <v>6216417</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123322284</v>
+        <v>123330321</v>
       </c>
       <c r="B16" t="n">
-        <v>57497</v>
+        <v>95323</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,57 +2253,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384701</v>
+        <v>384869</v>
       </c>
       <c r="R16" t="n">
-        <v>6216470</v>
+        <v>6216249</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,24 +2314,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,19 +2331,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330282</v>
+        <v>123330194</v>
       </c>
       <c r="B17" t="n">
         <v>95323</v>
@@ -2414,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384686</v>
+        <v>384879</v>
       </c>
       <c r="R17" t="n">
-        <v>6216321</v>
+        <v>6216271</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2476,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330199</v>
+        <v>123330315</v>
       </c>
       <c r="B18" t="n">
         <v>95323</v>
@@ -2516,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384747</v>
+        <v>384685</v>
       </c>
       <c r="R18" t="n">
-        <v>6216370</v>
+        <v>6216404</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2571,17 +2540,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330311</v>
+        <v>123330196</v>
       </c>
       <c r="B19" t="n">
-        <v>95323</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,25 +2559,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,13 +2587,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384830</v>
+        <v>384879</v>
       </c>
       <c r="R19" t="n">
-        <v>6216253</v>
+        <v>6216271</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,17 +2642,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330301</v>
+        <v>123330210</v>
       </c>
       <c r="B20" t="n">
-        <v>77124</v>
+        <v>95323</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,25 +2661,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1342</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384718</v>
+        <v>384737</v>
       </c>
       <c r="R20" t="n">
-        <v>6216416</v>
+        <v>6216302</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2758,11 +2727,6 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2780,17 +2744,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330271</v>
+        <v>123330269</v>
       </c>
       <c r="B21" t="n">
-        <v>80423</v>
+        <v>96759</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,21 +2767,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2889,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123330248</v>
+        <v>123322284</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>57497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2905,16 +2869,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2922,20 +2886,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384801</v>
+        <v>384701</v>
       </c>
       <c r="R22" t="n">
-        <v>6216415</v>
+        <v>6216470</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2962,9 +2942,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2979,22 +2974,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330299</v>
+        <v>123330229</v>
       </c>
       <c r="B23" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3007,21 +3002,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3031,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384718</v>
+        <v>384694</v>
       </c>
       <c r="R23" t="n">
-        <v>6216416</v>
+        <v>6216418</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3093,7 +3088,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330187</v>
+        <v>123330199</v>
       </c>
       <c r="B24" t="n">
         <v>95323</v>
@@ -3133,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384730</v>
+        <v>384747</v>
       </c>
       <c r="R24" t="n">
-        <v>6216280</v>
+        <v>6216370</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3188,14 +3183,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330194</v>
+        <v>123330187</v>
       </c>
       <c r="B25" t="n">
         <v>95323</v>
@@ -3235,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384879</v>
+        <v>384730</v>
       </c>
       <c r="R25" t="n">
-        <v>6216271</v>
+        <v>6216280</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3290,17 +3285,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330190</v>
+        <v>123330301</v>
       </c>
       <c r="B26" t="n">
-        <v>95323</v>
+        <v>77124</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3309,25 +3304,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3337,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384703</v>
+        <v>384718</v>
       </c>
       <c r="R26" t="n">
-        <v>6216448</v>
+        <v>6216416</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3375,6 +3370,11 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3392,17 +3392,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330284</v>
+        <v>123330259</v>
       </c>
       <c r="B27" t="n">
-        <v>57861</v>
+        <v>96759</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384686</v>
+        <v>384863</v>
       </c>
       <c r="R27" t="n">
-        <v>6216321</v>
+        <v>6216260</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3494,17 +3494,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330229</v>
+        <v>123330284</v>
       </c>
       <c r="B28" t="n">
-        <v>95323</v>
+        <v>57861</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,21 +3517,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384694</v>
+        <v>384686</v>
       </c>
       <c r="R28" t="n">
-        <v>6216418</v>
+        <v>6216321</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3596,17 +3596,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330269</v>
+        <v>123330271</v>
       </c>
       <c r="B29" t="n">
-        <v>96759</v>
+        <v>80423</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330210</v>
+        <v>123330248</v>
       </c>
       <c r="B30" t="n">
-        <v>95323</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3717,25 +3717,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384737</v>
+        <v>384801</v>
       </c>
       <c r="R30" t="n">
-        <v>6216302</v>
+        <v>6216415</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330257</v>
+        <v>123330282</v>
       </c>
       <c r="B31" t="n">
-        <v>95412</v>
+        <v>95323</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384724</v>
+        <v>384686</v>
       </c>
       <c r="R31" t="n">
-        <v>6216417</v>
+        <v>6216321</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115438370</v>
+        <v>115438235</v>
       </c>
       <c r="B2" t="n">
-        <v>57412</v>
+        <v>57281</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Syd Kumle, Sk</t>
+          <t>Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385178</v>
+        <v>384916</v>
       </c>
       <c r="R2" t="n">
-        <v>6216544</v>
+        <v>6216524</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,22 +753,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,17 +788,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115438235</v>
+        <v>123048253</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
+        <v>57641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,28 +828,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Sk</t>
+          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384916</v>
+        <v>384791</v>
       </c>
       <c r="R3" t="n">
-        <v>6216524</v>
+        <v>6216539</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123048253</v>
+        <v>123043424</v>
       </c>
       <c r="B4" t="n">
         <v>57641</v>
@@ -948,7 +950,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -961,17 +967,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Skogshyddan S Kriks, Sk</t>
+          <t>Forsby skog, Forsby skog, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>384791</v>
+        <v>384579</v>
       </c>
       <c r="R4" t="n">
-        <v>6216539</v>
+        <v>6216441</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123043424</v>
+        <v>123041890</v>
       </c>
       <c r="B5" t="n">
         <v>57641</v>
@@ -1091,13 +1097,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>384579</v>
+        <v>384833</v>
       </c>
       <c r="R5" t="n">
-        <v>6216441</v>
+        <v>6216338</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,19 +1130,9 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041890</v>
+        <v>123110343</v>
       </c>
       <c r="B6" t="n">
-        <v>57641</v>
+        <v>58169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,20 +1171,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1198,32 +1194,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Forsby skog, Forsby skog, Sk</t>
+          <t>Skogshyddan S Kriks, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>384833</v>
+        <v>384916</v>
       </c>
       <c r="R6" t="n">
-        <v>6216338</v>
+        <v>6216524</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,9 +1244,19 @@
           <t>2025-03-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,17 +1276,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123110343</v>
+        <v>123322288</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>57642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,20 +1295,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1314,30 +1318,30 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogshyddan S Kriks, Sk</t>
+          <t>Krika 2, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>384916</v>
+        <v>384803</v>
       </c>
       <c r="R7" t="n">
-        <v>6216524</v>
+        <v>6216452</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,22 +1365,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,22 +1395,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123322288</v>
+        <v>123330258</v>
       </c>
       <c r="B8" t="n">
-        <v>57642</v>
+        <v>96759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,53 +1419,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krika 2, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>384803</v>
+        <v>384724</v>
       </c>
       <c r="R8" t="n">
-        <v>6216452</v>
+        <v>6216417</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,19 +1480,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,22 +1497,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123330258</v>
+        <v>123330311</v>
       </c>
       <c r="B9" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,21 +1525,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1567,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>384724</v>
+        <v>384830</v>
       </c>
       <c r="R9" t="n">
-        <v>6216417</v>
+        <v>6216253</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1622,14 +1604,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123330311</v>
+        <v>123330190</v>
       </c>
       <c r="B10" t="n">
         <v>95323</v>
@@ -1669,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384830</v>
+        <v>384703</v>
       </c>
       <c r="R10" t="n">
-        <v>6216253</v>
+        <v>6216448</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1724,17 +1706,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123330190</v>
+        <v>123330226</v>
       </c>
       <c r="B11" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384703</v>
+        <v>384798</v>
       </c>
       <c r="R11" t="n">
-        <v>6216448</v>
+        <v>6216268</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1826,14 +1808,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123330226</v>
+        <v>123330299</v>
       </c>
       <c r="B12" t="n">
         <v>96759</v>
@@ -1873,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384798</v>
+        <v>384718</v>
       </c>
       <c r="R12" t="n">
-        <v>6216268</v>
+        <v>6216416</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1928,17 +1910,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123330299</v>
+        <v>123330183</v>
       </c>
       <c r="B13" t="n">
-        <v>96759</v>
+        <v>95323</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384718</v>
+        <v>384696</v>
       </c>
       <c r="R13" t="n">
-        <v>6216416</v>
+        <v>6216241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2030,17 +2012,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123330183</v>
+        <v>123330257</v>
       </c>
       <c r="B14" t="n">
-        <v>95323</v>
+        <v>95412</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>384696</v>
+        <v>384724</v>
       </c>
       <c r="R14" t="n">
-        <v>6216241</v>
+        <v>6216417</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2139,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123330257</v>
+        <v>123330321</v>
       </c>
       <c r="B15" t="n">
-        <v>95412</v>
+        <v>95323</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>384724</v>
+        <v>384869</v>
       </c>
       <c r="R15" t="n">
-        <v>6216417</v>
+        <v>6216249</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2234,14 +2216,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123330321</v>
+        <v>123330194</v>
       </c>
       <c r="B16" t="n">
         <v>95323</v>
@@ -2281,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>384869</v>
+        <v>384879</v>
       </c>
       <c r="R16" t="n">
-        <v>6216249</v>
+        <v>6216271</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2336,14 +2318,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123330194</v>
+        <v>123330315</v>
       </c>
       <c r="B17" t="n">
         <v>95323</v>
@@ -2383,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>384879</v>
+        <v>384685</v>
       </c>
       <c r="R17" t="n">
-        <v>6216271</v>
+        <v>6216404</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2438,17 +2420,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123330315</v>
+        <v>123330196</v>
       </c>
       <c r="B18" t="n">
-        <v>95323</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,25 +2439,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,13 +2467,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>384685</v>
+        <v>384879</v>
       </c>
       <c r="R18" t="n">
-        <v>6216404</v>
+        <v>6216271</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2547,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123330196</v>
+        <v>123330210</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2559,25 +2541,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2587,13 +2569,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>384879</v>
+        <v>384737</v>
       </c>
       <c r="R19" t="n">
-        <v>6216271</v>
+        <v>6216302</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123330210</v>
+        <v>123330269</v>
       </c>
       <c r="B20" t="n">
-        <v>95323</v>
+        <v>96759</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2689,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>384737</v>
+        <v>384715</v>
       </c>
       <c r="R20" t="n">
-        <v>6216302</v>
+        <v>6216422</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2744,17 +2726,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123330269</v>
+        <v>123322284</v>
       </c>
       <c r="B21" t="n">
-        <v>96759</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,41 +2745,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>100048</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Forsby, Sk</t>
+          <t>Krika 1, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>384715</v>
+        <v>384701</v>
       </c>
       <c r="R21" t="n">
-        <v>6216422</v>
+        <v>6216470</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,9 +2822,24 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2841,22 +2854,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123322284</v>
+        <v>123330229</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>95323</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2865,57 +2878,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100048</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Krika 1, Sk</t>
+          <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>384701</v>
+        <v>384694</v>
       </c>
       <c r="R22" t="n">
-        <v>6216470</v>
+        <v>6216418</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2942,24 +2939,9 @@
           <t>2025-03-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,19 +2956,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123330229</v>
+        <v>123330199</v>
       </c>
       <c r="B23" t="n">
         <v>95323</v>
@@ -3026,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>384694</v>
+        <v>384747</v>
       </c>
       <c r="R23" t="n">
-        <v>6216418</v>
+        <v>6216370</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3081,14 +3063,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123330199</v>
+        <v>123330187</v>
       </c>
       <c r="B24" t="n">
         <v>95323</v>
@@ -3128,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>384747</v>
+        <v>384730</v>
       </c>
       <c r="R24" t="n">
-        <v>6216370</v>
+        <v>6216280</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3190,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123330187</v>
+        <v>123330301</v>
       </c>
       <c r="B25" t="n">
-        <v>95323</v>
+        <v>77124</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,25 +3184,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2810</v>
+        <v>1342</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>384730</v>
+        <v>384718</v>
       </c>
       <c r="R25" t="n">
-        <v>6216280</v>
+        <v>6216416</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3266,6 +3248,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3292,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123330301</v>
+        <v>123330259</v>
       </c>
       <c r="B26" t="n">
-        <v>77124</v>
+        <v>96759</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3304,25 +3291,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3332,10 +3319,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>384718</v>
+        <v>384863</v>
       </c>
       <c r="R26" t="n">
-        <v>6216416</v>
+        <v>6216260</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3368,11 +3355,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Tre bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123330259</v>
+        <v>123330284</v>
       </c>
       <c r="B27" t="n">
-        <v>96759</v>
+        <v>57861</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3415,21 +3397,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3439,13 +3421,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>384863</v>
+        <v>384686</v>
       </c>
       <c r="R27" t="n">
-        <v>6216260</v>
+        <v>6216321</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3501,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123330284</v>
+        <v>123330271</v>
       </c>
       <c r="B28" t="n">
-        <v>57861</v>
+        <v>80423</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,21 +3499,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,13 +3523,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>384686</v>
+        <v>384715</v>
       </c>
       <c r="R28" t="n">
-        <v>6216321</v>
+        <v>6216422</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3596,17 +3578,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123330271</v>
+        <v>123330248</v>
       </c>
       <c r="B29" t="n">
-        <v>80423</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3615,25 +3597,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3643,13 +3625,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>384715</v>
+        <v>384801</v>
       </c>
       <c r="R29" t="n">
-        <v>6216422</v>
+        <v>6216415</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3705,10 +3687,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123330248</v>
+        <v>123330282</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3717,25 +3699,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,13 +3727,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>384801</v>
+        <v>384686</v>
       </c>
       <c r="R30" t="n">
-        <v>6216415</v>
+        <v>6216321</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3800,21 +3782,21 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123330282</v>
+        <v>123330192</v>
       </c>
       <c r="B31" t="n">
-        <v>95323</v>
+        <v>96707</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3823,21 +3805,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3847,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>384686</v>
+        <v>384693</v>
       </c>
       <c r="R31" t="n">
-        <v>6216321</v>
+        <v>6216445</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3902,60 +3884,63 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Salomon, Suvi Sivula, Stefan Phalagorn Bergström, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123330192</v>
+        <v>123383860</v>
       </c>
       <c r="B32" t="n">
-        <v>96707</v>
+        <v>91416</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2569</v>
+        <v>2023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>384693</v>
+        <v>384864</v>
       </c>
       <c r="R32" t="n">
-        <v>6216445</v>
+        <v>6216297</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3993,28 +3978,49 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
+          <t>Stefan Phalagorn Bergström, Suvi Sivula, Lars Salomon, Jan Svensson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123383860</v>
+        <v>123330306</v>
       </c>
       <c r="B33" t="n">
-        <v>91416</v>
+        <v>78610</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4027,40 +4033,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2023</v>
+        <v>924</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Forsby, Sk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>384864</v>
+        <v>384733</v>
       </c>
       <c r="R33" t="n">
-        <v>6216297</v>
+        <v>6216385</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4092,155 +4095,32 @@
           <t>2025-03-20</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>En bål mellan stora bålar med porlav</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Fagus sylvatica</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Suvi Sivula, Lars Salomon, Jan Svensson</t>
+          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>123330306</v>
-      </c>
-      <c r="B34" t="n">
-        <v>78610</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>924</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Bokkantlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Lecanora glabrata</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Malme</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Forsby, Sk</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>384733</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6216385</v>
-      </c>
-      <c r="S34" t="n">
-        <v>15</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Västra Sönnarslöv</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>En bål mellan stora bålar med porlav</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Lars Salomon</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Lars Salomon, Jan Svensson, Stefan Phalagorn Bergström, Suvi Sivula</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2762-2024 artfynd.xlsx
+++ b/artfynd/A 2762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123383813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330306</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123383860</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330192</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330259</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330269</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330299</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330257</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330183</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330184</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,6 +2162,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330187</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330190</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2286,6 +2366,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330194</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2383,6 +2468,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330199</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2480,6 +2570,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330210</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2577,6 +2672,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330229</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330282</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2771,6 +2876,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330311</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2868,6 +2978,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330315</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2965,6 +3080,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330321</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3093,6 +3213,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123322284</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3208,6 +3333,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115438235</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3305,6 +3435,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330196</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330248</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3499,6 +3639,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330284</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3610,6 +3755,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123041890</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3731,6 +3881,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123043424</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3848,6 +4003,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123048253</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3967,6 +4127,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123322288</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4086,6 +4251,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123110343</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4183,8 +4353,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123330271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>